--- a/excel/LoadingData.xlsx
+++ b/excel/LoadingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95516536-CD02-E248-A074-9DDC2CE79090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2353860-0E16-5842-8A91-143947690AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14240" yWindow="2620" windowWidth="19820" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9580" yWindow="2620" windowWidth="19820" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Loading" sheetId="1" r:id="rId1"/>
@@ -196,6 +196,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -215,6 +216,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1]</t>
@@ -240,6 +242,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>_</t>
@@ -259,6 +262,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1]</t>
@@ -296,9 +300,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>img_myhome_background</t>
-  </si>
-  <si>
     <t>CottonCandyShop</t>
   </si>
   <si>
@@ -307,6 +308,9 @@
   <si>
     <t>BeddingShop</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>loading01</t>
   </si>
 </sst>
 </file>
@@ -448,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -463,7 +467,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -727,7 +730,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -741,7 +744,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -755,38 +758,38 @@
         <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="13">
